--- a/submissions/10-carton-bid-evaluation/inputs/bid_tabulation_itb_2026_17.xlsx
+++ b/submissions/10-carton-bid-evaluation/inputs/bid_tabulation_itb_2026_17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A649E473-8A5E-C742-BBA5-4E5A9789B772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0618B4C9-7D1D-684A-BCC9-6DE2BA1021A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,12 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="104">
   <si>
     <t>ITB 2026-17, corrugated shipping cartons, annual requirement; bids as opened October 6, 2026, 10:00, Nordvik Manufacturing purchasing office</t>
   </si>
   <si>
-    <t>Unit prices in dollars per carton and extensions in dollars as written on each bid form; tooling as written.</t>
+    <t>Unit prices in dollars per carton and extensions in dollars as written on each bid form; tooling as written. Six bids received; listed in alphabetical order.</t>
   </si>
   <si>
     <t>ITEM</t>
@@ -45,6 +45,30 @@
     <t>DESCRIPTION</t>
   </si>
   <si>
+    <t>BRANNOCK_UNIT</t>
+  </si>
+  <si>
+    <t>BRANNOCK_EXTENSION</t>
+  </si>
+  <si>
+    <t>HALVARD_UNIT</t>
+  </si>
+  <si>
+    <t>HALVARD_EXTENSION</t>
+  </si>
+  <si>
+    <t>LOKEN_VIK_UNIT</t>
+  </si>
+  <si>
+    <t>LOKEN_VIK_EXTENSION</t>
+  </si>
+  <si>
+    <t>OTTER_TAIL_UNIT</t>
+  </si>
+  <si>
+    <t>OTTER_TAIL_EXTENSION</t>
+  </si>
+  <si>
     <t>PEMBERTON_UNIT</t>
   </si>
   <si>
@@ -57,18 +81,6 @@
     <t>RIDGECREST_EXTENSION</t>
   </si>
   <si>
-    <t>BRANNOCK_UNIT</t>
-  </si>
-  <si>
-    <t>BRANNOCK_EXTENSION</t>
-  </si>
-  <si>
-    <t>HALVARD_UNIT</t>
-  </si>
-  <si>
-    <t>HALVARD_EXTENSION</t>
-  </si>
-  <si>
     <t>RSC 24 x 18 x 12, 200 lb test C flute, kraft, unprinted</t>
   </si>
   <si>
@@ -90,7 +102,7 @@
     <t>Total bid as written</t>
   </si>
   <si>
-    <t>Bidder terms and submittals as received, ITB 2026-17</t>
+    <t>Bidder terms and submittals as marked on the bid forms, ITB 2026-17, as opened</t>
   </si>
   <si>
     <t>BIDDER</t>
@@ -111,21 +123,96 @@
     <t>BID_BOND_5_PCT</t>
   </si>
   <si>
+    <t>BOND_FORM</t>
+  </si>
+  <si>
     <t>ADDENDA_ACKNOWLEDGED</t>
   </si>
   <si>
     <t>SAMPLES_RECEIVED</t>
   </si>
   <si>
-    <t>PRICE_HOLD_STATED</t>
-  </si>
-  <si>
-    <t>EXCEPTIONS_AND_ALTERNATES</t>
-  </si>
-  <si>
     <t>RECEIVED</t>
   </si>
   <si>
+    <t>Brannock Box Company</t>
+  </si>
+  <si>
+    <t>Rockford</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>Net 30</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Surety bond</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>10/05/2026 16:02</t>
+  </si>
+  <si>
+    <t>Halvard Corrugated</t>
+  </si>
+  <si>
+    <t>Fargo</t>
+  </si>
+  <si>
+    <t>ND</t>
+  </si>
+  <si>
+    <t>2% 30, net 60</t>
+  </si>
+  <si>
+    <t>1, 2</t>
+  </si>
+  <si>
+    <t>10/06/2026 09:58</t>
+  </si>
+  <si>
+    <t>Loken &amp; Vik Container</t>
+  </si>
+  <si>
+    <t>Sioux Falls</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>2% 20, net 45</t>
+  </si>
+  <si>
+    <t>Cashier's check, $6,655.10, no. 4471820</t>
+  </si>
+  <si>
+    <t>10/06/2026 09:20</t>
+  </si>
+  <si>
+    <t>Otter Tail Corrugated</t>
+  </si>
+  <si>
+    <t>Fergus Falls</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>1% 15, net 30</t>
+  </si>
+  <si>
+    <t>10/06/2026 08:52</t>
+  </si>
+  <si>
     <t>Pemberton Container</t>
   </si>
   <si>
@@ -135,24 +222,9 @@
     <t>WI</t>
   </si>
   <si>
-    <t>Destination</t>
-  </si>
-  <si>
     <t>2% 10, net 30</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>1, 2</t>
-  </si>
-  <si>
-    <t>12 months as required</t>
-  </si>
-  <si>
-    <t>None. Alternate bid submitted for item 4 at 200 lb test doublewall, 1.512 per carton, if acceptable.</t>
-  </si>
-  <si>
     <t>10/06/2026 09:41</t>
   </si>
   <si>
@@ -171,49 +243,10 @@
     <t>1% 20, net 45</t>
   </si>
   <si>
-    <t>None.</t>
-  </si>
-  <si>
     <t>10/06/2026 08:15</t>
   </si>
   <si>
-    <t>Brannock Box Company</t>
-  </si>
-  <si>
-    <t>Rockford</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>Net 30</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>10/05/2026 16:02</t>
-  </si>
-  <si>
-    <t>Halvard Corrugated</t>
-  </si>
-  <si>
-    <t>Fargo</t>
-  </si>
-  <si>
-    <t>ND</t>
-  </si>
-  <si>
-    <t>2% 30, net 60</t>
-  </si>
-  <si>
-    <t>Prices firm for 6 months from award; thereafter subject to paper index adjustment</t>
-  </si>
-  <si>
-    <t>Exception to ITB section 4.3: prices firm for 6 months, then adjusted quarterly to the Pulp and Paper Week linerboard index.</t>
-  </si>
-  <si>
-    <t>10/06/2026 09:58</t>
+    <t>Pricing conditions, exceptions and alternates are in each bidder's form and letter in the bid file; the tabulation records what the bid form boxes carry.</t>
   </si>
   <si>
     <t>Nordvik inbound freight schedule for bid evaluation, dollars per hundredweight to Alexandria, Minnesota, effective July 1, 2026</t>
@@ -228,9 +261,6 @@
     <t>NOTE</t>
   </si>
   <si>
-    <t>MN</t>
-  </si>
-  <si>
     <t>Intrastate, common carrier</t>
   </si>
   <si>
@@ -246,9 +276,6 @@
     <t>Common carrier, Fargo gateway</t>
   </si>
   <si>
-    <t>SD</t>
-  </si>
-  <si>
     <t>Common carrier, Sioux Falls gateway</t>
   </si>
   <si>
@@ -258,10 +285,19 @@
     <t>Common carrier, Omaha gateway</t>
   </si>
   <si>
-    <t>The schedule is applied to the shipping weight of the annual quantity at the item weights on the Item Weights sheet, in hundredweight, for any bid offered FOB origin. No minimum charge applies to the evaluation.</t>
-  </si>
-  <si>
-    <t>Shipping weight per carton, from the ITB carton specifications, pounds</t>
+    <t>The schedule is applied to the shipping weight of the annual quantity at the current item weights on the Item Weights sheet, in hundredweight, for any bid offered FOB origin. No minimum charge applies to the evaluation.</t>
+  </si>
+  <si>
+    <t>Shipping weight per carton by drawing revision, from the drawing set NM-CTN-26 as issued and amended, pounds</t>
+  </si>
+  <si>
+    <t>DRAWING</t>
+  </si>
+  <si>
+    <t>REV</t>
+  </si>
+  <si>
+    <t>STATUS</t>
   </si>
   <si>
     <t>LB_PER_CARTON</t>
@@ -271,6 +307,42 @@
   </si>
   <si>
     <t>PALLETS_PER_TRUCKLOAD</t>
+  </si>
+  <si>
+    <t>NM-CTN-26-01</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>NM-CTN-26-02</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Current, addendum 1</t>
+  </si>
+  <si>
+    <t>NM-CTN-26-03</t>
+  </si>
+  <si>
+    <t>NM-CTN-26-04</t>
+  </si>
+  <si>
+    <t>NM-CTN-26-05</t>
+  </si>
+  <si>
+    <t>Superseded, addendum 2</t>
+  </si>
+  <si>
+    <t>Current, addendum 2</t>
+  </si>
+  <si>
+    <t>A superseded revision is kept on the sheet for the record of the drawing set; the current revision is the one the evaluation uses.</t>
   </si>
 </sst>
 </file>
@@ -280,13 +352,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -326,14 +403,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -649,246 +728,336 @@
     <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.571</v>
+      </c>
+      <c r="D5" s="5">
+        <v>34260</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.605</v>
+      </c>
+      <c r="F5" s="5">
+        <v>36300</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.609</v>
+      </c>
+      <c r="H5" s="5">
+        <v>36540</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.601</v>
+      </c>
+      <c r="J5" s="5">
+        <v>36060</v>
+      </c>
+      <c r="K5" s="4">
         <v>0.612</v>
       </c>
-      <c r="D5" s="4">
+      <c r="L5" s="5">
         <v>36720</v>
       </c>
-      <c r="E5" s="3">
+      <c r="M5" s="4">
         <v>0.598</v>
       </c>
-      <c r="F5" s="4">
+      <c r="N5" s="5">
         <v>35880</v>
       </c>
-      <c r="G5" s="3">
-        <v>0.571</v>
-      </c>
-      <c r="H5" s="4">
-        <v>34260</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0.605</v>
-      </c>
-      <c r="J5" s="4">
-        <v>36300</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.398</v>
+      </c>
+      <c r="D6" s="5">
+        <v>33432</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.412</v>
+      </c>
+      <c r="F6" s="5">
+        <v>34608</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.409</v>
+      </c>
+      <c r="H6" s="5">
+        <v>34356</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.411</v>
+      </c>
+      <c r="J6" s="5">
+        <v>34524</v>
+      </c>
+      <c r="K6" s="4">
         <v>0.418</v>
       </c>
-      <c r="D6" s="4">
+      <c r="L6" s="5">
         <v>45112</v>
       </c>
-      <c r="E6" s="3">
+      <c r="M6" s="4">
         <v>0.405</v>
       </c>
-      <c r="F6" s="4">
+      <c r="N6" s="5">
         <v>34020</v>
       </c>
-      <c r="G6" s="3">
-        <v>0.398</v>
-      </c>
-      <c r="H6" s="4">
-        <v>33432</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.412</v>
-      </c>
-      <c r="J6" s="4">
-        <v>34608</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7">
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.276</v>
+      </c>
+      <c r="D7" s="5">
+        <v>13248</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.288</v>
+      </c>
+      <c r="F7" s="5">
+        <v>10368</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.287</v>
+      </c>
+      <c r="H7" s="5">
+        <v>10332</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.283</v>
+      </c>
+      <c r="J7" s="5">
+        <v>10188</v>
+      </c>
+      <c r="K7" s="4">
         <v>0.294</v>
       </c>
-      <c r="D7" s="4">
+      <c r="L7" s="5">
         <v>10584</v>
       </c>
-      <c r="E7" s="3">
+      <c r="M7" s="4">
         <v>0.281</v>
       </c>
-      <c r="F7" s="4">
+      <c r="N7" s="5">
         <v>10116</v>
       </c>
-      <c r="G7" s="3">
-        <v>0.276</v>
-      </c>
-      <c r="H7" s="4">
-        <v>13248</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0.288</v>
-      </c>
-      <c r="J7" s="4">
-        <v>10368</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8">
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1.655</v>
+      </c>
+      <c r="D8" s="5">
+        <v>19860</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1.702</v>
+      </c>
+      <c r="F8" s="5">
+        <v>20424</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1.712</v>
+      </c>
+      <c r="H8" s="5">
+        <v>20544</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1.694</v>
+      </c>
+      <c r="J8" s="5">
+        <v>20328</v>
+      </c>
+      <c r="K8" s="4">
         <v>1.735</v>
       </c>
-      <c r="D8" s="4">
+      <c r="L8" s="5">
         <v>20820</v>
       </c>
-      <c r="E8" s="3">
+      <c r="M8" s="4">
         <v>1.69</v>
       </c>
-      <c r="F8" s="4">
+      <c r="N8" s="5">
         <v>20280</v>
       </c>
-      <c r="G8" s="3">
-        <v>1.655</v>
-      </c>
-      <c r="H8" s="4">
-        <v>19860</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1.702</v>
-      </c>
-      <c r="J8" s="4">
-        <v>20424</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9">
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="D9" s="5">
+        <v>28200</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.972</v>
+      </c>
+      <c r="F9" s="5">
+        <v>29160</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.976</v>
+      </c>
+      <c r="H9" s="5">
+        <v>29280</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.969</v>
+      </c>
+      <c r="J9" s="5">
+        <v>29070</v>
+      </c>
+      <c r="K9" s="4">
         <v>0.988</v>
       </c>
-      <c r="D9" s="4">
+      <c r="L9" s="5">
         <v>29640</v>
       </c>
-      <c r="E9" s="3">
+      <c r="M9" s="4">
         <v>0.965</v>
       </c>
-      <c r="F9" s="4">
+      <c r="N9" s="5">
         <v>28950</v>
       </c>
-      <c r="G9" s="3">
-        <v>0.94</v>
-      </c>
-      <c r="H9" s="4">
-        <v>28200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0.972</v>
-      </c>
-      <c r="J9" s="4">
-        <v>29160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="4">
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1500</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1600</v>
+      </c>
+      <c r="H10" s="5">
+        <v>2050</v>
+      </c>
+      <c r="J10" s="5">
+        <v>1725</v>
+      </c>
+      <c r="L10" s="5">
         <v>1850</v>
       </c>
-      <c r="F10" s="4">
+      <c r="N10" s="5">
         <v>2400</v>
       </c>
-      <c r="H10" s="4">
-        <v>1500</v>
-      </c>
-      <c r="J10" s="4">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="4">
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="7">
         <f>SUM(D5:D10)</f>
+        <v>130500</v>
+      </c>
+      <c r="F11" s="7">
+        <f>SUM(F5:F10)</f>
+        <v>132460</v>
+      </c>
+      <c r="H11" s="7">
+        <f>SUM(H5:H10)</f>
+        <v>133102</v>
+      </c>
+      <c r="J11" s="7">
+        <f>SUM(J5:J10)</f>
+        <v>131895</v>
+      </c>
+      <c r="L11" s="7">
+        <f>SUM(L5:L10)</f>
         <v>144726</v>
       </c>
-      <c r="F11" s="4">
-        <f>SUM(F5:F10)</f>
+      <c r="N11" s="7">
+        <f>SUM(N5:N10)</f>
         <v>131646</v>
-      </c>
-      <c r="H11" s="4">
-        <f>SUM(H5:H10)</f>
-        <v>130500</v>
-      </c>
-      <c r="J11" s="4">
-        <f>SUM(J5:J10)</f>
-        <v>132460</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -907,191 +1076,244 @@
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
-    <col min="10" max="10" width="70" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="2" t="s">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
+      <c r="I3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
+      <c r="J3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F4" t="s">
+      <c r="C4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G4" t="s">
+      <c r="D4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J4" t="s">
+      <c r="F4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K4" t="s">
+      <c r="G4" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="H4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B5" t="s">
+      <c r="I4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E5" t="s">
+      <c r="C5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="D5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="E5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K5" t="s">
+      <c r="F5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="I5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="C6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="D6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="F6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="H6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="C7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="D7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="E7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J7" t="s">
+      <c r="F7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K7" t="s">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>60</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1104,106 +1326,106 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="8">
+        <v>4.85</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="6">
-        <v>3.4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="6">
-        <v>4.85</v>
-      </c>
-      <c r="C5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="B6" s="8">
         <v>5.1</v>
       </c>
-      <c r="C6" t="s">
-        <v>68</v>
+      <c r="C6" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="A7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="8">
         <v>5.6</v>
       </c>
-      <c r="C7" t="s">
-        <v>69</v>
+      <c r="C7" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="6">
+      <c r="A8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="8">
         <v>4.2</v>
       </c>
-      <c r="C8" t="s">
-        <v>70</v>
+      <c r="C8" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="6">
+      <c r="A9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="8">
         <v>4.6</v>
       </c>
-      <c r="C9" t="s">
-        <v>72</v>
+      <c r="C9" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="A10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="8">
         <v>5.35</v>
       </c>
-      <c r="C10" t="s">
-        <v>74</v>
+      <c r="C10" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>75</v>
+      <c r="A12" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1213,96 +1435,187 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="B3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="8">
         <v>0.9</v>
       </c>
-      <c r="C4">
+      <c r="F4" s="2">
         <v>400</v>
       </c>
-      <c r="D4">
+      <c r="G4" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="8">
         <v>0.55</v>
       </c>
-      <c r="C5">
+      <c r="F5" s="2">
         <v>600</v>
       </c>
-      <c r="D5">
+      <c r="G5" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="8">
         <v>0.3</v>
       </c>
-      <c r="C6">
+      <c r="F6" s="2">
         <v>1200</v>
       </c>
-      <c r="D6">
+      <c r="G6" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="8">
         <v>2.6</v>
       </c>
-      <c r="C7">
+      <c r="F7" s="2">
         <v>150</v>
       </c>
-      <c r="D7">
+      <c r="G7" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="8">
         <v>1.4</v>
       </c>
-      <c r="C8">
+      <c r="F8" s="2">
         <v>250</v>
       </c>
-      <c r="D8">
+      <c r="G8" s="2">
         <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.65</v>
+      </c>
+      <c r="F9" s="2">
+        <v>250</v>
+      </c>
+      <c r="G9" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/submissions/10-carton-bid-evaluation/inputs/bid_tabulation_itb_2026_17.xlsx
+++ b/submissions/10-carton-bid-evaluation/inputs/bid_tabulation_itb_2026_17.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0618B4C9-7D1D-684A-BCC9-6DE2BA1021A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D5DAD6-4945-5741-B597-FC2D3FEDF328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,12 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="131">
   <si>
     <t>ITB 2026-17, corrugated shipping cartons, annual requirement; bids as opened October 6, 2026, 10:00, Nordvik Manufacturing purchasing office</t>
   </si>
   <si>
-    <t>Unit prices in dollars per carton and extensions in dollars as written on each bid form; tooling as written. Six bids received; listed in alphabetical order.</t>
+    <t>Unit prices in dollars per carton and extensions in dollars as written on each bid form; tooling as written. Eleven bids received; listed in alphabetical order.</t>
   </si>
   <si>
     <t>ITEM</t>
@@ -51,18 +51,36 @@
     <t>BRANNOCK_EXTENSION</t>
   </si>
   <si>
+    <t>DAHLGREN_UNIT</t>
+  </si>
+  <si>
+    <t>DAHLGREN_EXTENSION</t>
+  </si>
+  <si>
     <t>HALVARD_UNIT</t>
   </si>
   <si>
     <t>HALVARD_EXTENSION</t>
   </si>
   <si>
+    <t>KESSEL_UNIT</t>
+  </si>
+  <si>
+    <t>KESSEL_EXTENSION</t>
+  </si>
+  <si>
     <t>LOKEN_VIK_UNIT</t>
   </si>
   <si>
     <t>LOKEN_VIK_EXTENSION</t>
   </si>
   <si>
+    <t>MESABI_UNIT</t>
+  </si>
+  <si>
+    <t>MESABI_EXTENSION</t>
+  </si>
+  <si>
     <t>OTTER_TAIL_UNIT</t>
   </si>
   <si>
@@ -81,6 +99,18 @@
     <t>RIDGECREST_EXTENSION</t>
   </si>
   <si>
+    <t>THORSGARD_UNIT</t>
+  </si>
+  <si>
+    <t>THORSGARD_EXTENSION</t>
+  </si>
+  <si>
+    <t>WENZEL_KRAUSE_UNIT</t>
+  </si>
+  <si>
+    <t>WENZEL_KRAUSE_EXTENSION</t>
+  </si>
+  <si>
     <t>RSC 24 x 18 x 12, 200 lb test C flute, kraft, unprinted</t>
   </si>
   <si>
@@ -120,10 +150,10 @@
     <t>PAYMENT_TERMS</t>
   </si>
   <si>
-    <t>BID_BOND_5_PCT</t>
-  </si>
-  <si>
-    <t>BOND_FORM</t>
+    <t>BID_SECURITY_ENCLOSED</t>
+  </si>
+  <si>
+    <t>SECURITY_FORM</t>
   </si>
   <si>
     <t>ADDENDA_ACKNOWLEDGED</t>
@@ -132,9 +162,6 @@
     <t>SAMPLES_RECEIVED</t>
   </si>
   <si>
-    <t>RECEIVED</t>
-  </si>
-  <si>
     <t>Brannock Box Company</t>
   </si>
   <si>
@@ -159,7 +186,22 @@
     <t>1</t>
   </si>
   <si>
-    <t>10/05/2026 16:02</t>
+    <t>Dahlgren Paper Box Co.</t>
+  </si>
+  <si>
+    <t>St. Cloud</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>1% 30, net 45</t>
+  </si>
+  <si>
+    <t>Cashier's check, $4,904.75, no. 20871</t>
+  </si>
+  <si>
+    <t>1, 2</t>
   </si>
   <si>
     <t>Halvard Corrugated</t>
@@ -174,10 +216,16 @@
     <t>2% 30, net 60</t>
   </si>
   <si>
-    <t>1, 2</t>
-  </si>
-  <si>
-    <t>10/06/2026 09:58</t>
+    <t>Kessel Container Corp.</t>
+  </si>
+  <si>
+    <t>Des Moines</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>1% 20, net 30</t>
   </si>
   <si>
     <t>Loken &amp; Vik Container</t>
@@ -192,10 +240,16 @@
     <t>2% 20, net 45</t>
   </si>
   <si>
-    <t>Cashier's check, $6,655.10, no. 4471820</t>
-  </si>
-  <si>
-    <t>10/06/2026 09:20</t>
+    <t>Cashier's check, $5,060.70, no. 4471820</t>
+  </si>
+  <si>
+    <t>Mesabi Container Co.</t>
+  </si>
+  <si>
+    <t>Duluth</t>
+  </si>
+  <si>
+    <t>Origin, Duluth plant</t>
   </si>
   <si>
     <t>Otter Tail Corrugated</t>
@@ -204,15 +258,9 @@
     <t>Fergus Falls</t>
   </si>
   <si>
-    <t>MN</t>
-  </si>
-  <si>
     <t>1% 15, net 30</t>
   </si>
   <si>
-    <t>10/06/2026 08:52</t>
-  </si>
-  <si>
     <t>Pemberton Container</t>
   </si>
   <si>
@@ -225,25 +273,37 @@
     <t>2% 10, net 30</t>
   </si>
   <si>
-    <t>10/06/2026 09:41</t>
-  </si>
-  <si>
     <t>Ridgecrest Packaging</t>
   </si>
   <si>
     <t>Cedar Rapids</t>
   </si>
   <si>
-    <t>IA</t>
-  </si>
-  <si>
-    <t>Origin, Cedar Rapids plant</t>
+    <t>Origin, shipping plant</t>
   </si>
   <si>
     <t>1% 20, net 45</t>
   </si>
   <si>
-    <t>10/06/2026 08:15</t>
+    <t>Thorsgard Box &amp; Label</t>
+  </si>
+  <si>
+    <t>Moorhead</t>
+  </si>
+  <si>
+    <t>2% 25, net 45</t>
+  </si>
+  <si>
+    <t>Wenzel &amp; Krause Corrugated</t>
+  </si>
+  <si>
+    <t>La Crosse</t>
+  </si>
+  <si>
+    <t>2% 20, net 30</t>
+  </si>
+  <si>
+    <t>Cashier's check, $5,300.00, no. 553106</t>
   </si>
   <si>
     <t>Pricing conditions, exceptions and alternates are in each bidder's form and letter in the bid file; the tabulation records what the bid form boxes carry.</t>
@@ -285,7 +345,7 @@
     <t>Common carrier, Omaha gateway</t>
   </si>
   <si>
-    <t>The schedule is applied to the shipping weight of the annual quantity at the current item weights on the Item Weights sheet, in hundredweight, for any bid offered FOB origin. No minimum charge applies to the evaluation.</t>
+    <t>The schedule is applied to the shipping weight of the annual quantity at the item weights of the current drawing revisions on the Item Weights sheet, in hundredweight, for any bid offered FOB origin. No minimum charge applies to the evaluation.</t>
   </si>
   <si>
     <t>Shipping weight per carton by drawing revision, from the drawing set NM-CTN-26 as issued and amended, pounds</t>
@@ -297,7 +357,10 @@
     <t>REV</t>
   </si>
   <si>
-    <t>STATUS</t>
+    <t>REV_DATE</t>
+  </si>
+  <si>
+    <t>SIZE_AND_BOARD</t>
   </si>
   <si>
     <t>LB_PER_CARTON</t>
@@ -315,34 +378,52 @@
     <t>A</t>
   </si>
   <si>
-    <t>Current</t>
+    <t>08/21/2026</t>
+  </si>
+  <si>
+    <t>24 x 18 x 12, 200 lb test C flute</t>
   </si>
   <si>
     <t>NM-CTN-26-02</t>
   </si>
   <si>
+    <t>18 x 12 x 12, 32 ECT B flute</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
-    <t>Current, addendum 1</t>
+    <t>09/16/2026</t>
+  </si>
+  <si>
+    <t>18 x 12 x 10, 32 ECT B flute</t>
   </si>
   <si>
     <t>NM-CTN-26-03</t>
   </si>
   <si>
+    <t>12 x 9 x 4, 32 ECT E flute, white</t>
+  </si>
+  <si>
     <t>NM-CTN-26-04</t>
   </si>
   <si>
+    <t>36 x 24 x 24, 275 lb test doublewall</t>
+  </si>
+  <si>
     <t>NM-CTN-26-05</t>
   </si>
   <si>
-    <t>Superseded, addendum 2</t>
-  </si>
-  <si>
-    <t>Current, addendum 2</t>
-  </si>
-  <si>
-    <t>A superseded revision is kept on the sheet for the record of the drawing set; the current revision is the one the evaluation uses.</t>
+    <t>20 x 20 x 20, 32 ECT C flute, two-color</t>
+  </si>
+  <si>
+    <t>09/24/2026</t>
+  </si>
+  <si>
+    <t>20 x 20 x 20, 44 ECT C flute, two-color</t>
+  </si>
+  <si>
+    <t>Both revisions of a revised drawing are kept on the sheet for the record of the drawing set.</t>
   </si>
 </sst>
 </file>
@@ -352,7 +433,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,6 +449,17 @@
     <font>
       <b/>
       <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -403,7 +495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -413,6 +505,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -715,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -732,19 +827,29 @@
     <col min="12" max="12" width="22" customWidth="1"/>
     <col min="13" max="13" width="18" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="22" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="22" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="22" customWidth="1"/>
+    <col min="21" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="22" customWidth="1"/>
+    <col min="23" max="23" width="18" customWidth="1"/>
+    <col min="24" max="24" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -787,277 +892,492 @@
       <c r="N4" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C5" s="4">
         <v>0.571</v>
       </c>
       <c r="D5" s="5">
-        <v>34260</v>
+        <v>25695</v>
       </c>
       <c r="E5" s="4">
-        <v>0.605</v>
+        <v>0.591</v>
       </c>
       <c r="F5" s="5">
-        <v>36300</v>
+        <v>26595</v>
       </c>
       <c r="G5" s="4">
-        <v>0.609</v>
+        <v>0.594</v>
       </c>
       <c r="H5" s="5">
-        <v>36540</v>
+        <v>26730</v>
       </c>
       <c r="I5" s="4">
-        <v>0.601</v>
+        <v>0.59</v>
       </c>
       <c r="J5" s="5">
-        <v>36060</v>
+        <v>26550</v>
       </c>
       <c r="K5" s="4">
-        <v>0.612</v>
+        <v>0.598</v>
       </c>
       <c r="L5" s="5">
-        <v>36720</v>
+        <v>26910</v>
       </c>
       <c r="M5" s="4">
-        <v>0.598</v>
+        <v>0.562</v>
       </c>
       <c r="N5" s="5">
-        <v>35880</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+        <v>25290</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0.583</v>
+      </c>
+      <c r="P5" s="5">
+        <v>26235</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.602</v>
+      </c>
+      <c r="R5" s="5">
+        <v>27090</v>
+      </c>
+      <c r="S5" s="4">
+        <v>0.546</v>
+      </c>
+      <c r="T5" s="5">
+        <v>24570</v>
+      </c>
+      <c r="U5" s="4">
+        <v>0.604</v>
+      </c>
+      <c r="V5" s="5">
+        <v>27180</v>
+      </c>
+      <c r="W5" s="4">
+        <v>0.628</v>
+      </c>
+      <c r="X5" s="5">
+        <v>28260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4">
         <v>0.398</v>
       </c>
       <c r="D6" s="5">
-        <v>33432</v>
+        <v>25472</v>
       </c>
       <c r="E6" s="4">
-        <v>0.412</v>
+        <v>0.397</v>
       </c>
       <c r="F6" s="5">
-        <v>34608</v>
+        <v>25408</v>
       </c>
       <c r="G6" s="4">
-        <v>0.409</v>
+        <v>0.404</v>
       </c>
       <c r="H6" s="5">
-        <v>34356</v>
+        <v>25856</v>
       </c>
       <c r="I6" s="4">
-        <v>0.411</v>
+        <v>0.402</v>
       </c>
       <c r="J6" s="5">
-        <v>34524</v>
+        <v>25728</v>
       </c>
       <c r="K6" s="4">
-        <v>0.418</v>
+        <v>0.401</v>
       </c>
       <c r="L6" s="5">
-        <v>45112</v>
+        <v>25664</v>
       </c>
       <c r="M6" s="4">
-        <v>0.405</v>
+        <v>0.386</v>
       </c>
       <c r="N6" s="5">
-        <v>34020</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+        <v>24704</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0.399</v>
+      </c>
+      <c r="P6" s="5">
+        <v>25536</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.408</v>
+      </c>
+      <c r="R6" s="5">
+        <v>26912</v>
+      </c>
+      <c r="S6" s="4">
+        <v>0.37</v>
+      </c>
+      <c r="T6" s="5">
+        <v>23680</v>
+      </c>
+      <c r="U6" s="4">
+        <v>0.407</v>
+      </c>
+      <c r="V6" s="5">
+        <v>26048</v>
+      </c>
+      <c r="W6" s="4">
+        <v>0.428</v>
+      </c>
+      <c r="X6" s="5">
+        <v>27392</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4">
         <v>0.276</v>
       </c>
       <c r="D7" s="5">
-        <v>13248</v>
+        <v>9936</v>
       </c>
       <c r="E7" s="4">
+        <v>0.284</v>
+      </c>
+      <c r="F7" s="5">
+        <v>7668</v>
+      </c>
+      <c r="G7" s="4">
         <v>0.288</v>
       </c>
-      <c r="F7" s="5">
-        <v>10368</v>
-      </c>
-      <c r="G7" s="4">
+      <c r="H7" s="5">
+        <v>7776</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.285</v>
+      </c>
+      <c r="J7" s="5">
+        <v>7695</v>
+      </c>
+      <c r="K7" s="4">
         <v>0.287</v>
       </c>
-      <c r="H7" s="5">
-        <v>10332</v>
-      </c>
-      <c r="I7" s="4">
+      <c r="L7" s="5">
+        <v>7749</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0.268</v>
+      </c>
+      <c r="N7" s="5">
+        <v>7236</v>
+      </c>
+      <c r="O7" s="4">
         <v>0.283</v>
       </c>
-      <c r="J7" s="5">
-        <v>10188</v>
-      </c>
-      <c r="K7" s="4">
-        <v>0.294</v>
-      </c>
-      <c r="L7" s="5">
-        <v>10584</v>
-      </c>
-      <c r="M7" s="4">
+      <c r="P7" s="5">
+        <v>7641</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.289</v>
+      </c>
+      <c r="R7" s="5">
+        <v>7803</v>
+      </c>
+      <c r="S7" s="4">
+        <v>0.262</v>
+      </c>
+      <c r="T7" s="5">
+        <v>7074</v>
+      </c>
+      <c r="U7" s="4">
         <v>0.281</v>
       </c>
-      <c r="N7" s="5">
-        <v>10116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="V7" s="5">
+        <v>7587</v>
+      </c>
+      <c r="W7" s="4">
+        <v>0.301</v>
+      </c>
+      <c r="X7" s="5">
+        <v>8127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4">
         <v>1.655</v>
       </c>
       <c r="D8" s="5">
-        <v>19860</v>
+        <v>14895</v>
       </c>
       <c r="E8" s="4">
+        <v>1.688</v>
+      </c>
+      <c r="F8" s="5">
+        <v>15192</v>
+      </c>
+      <c r="G8" s="4">
         <v>1.702</v>
       </c>
-      <c r="F8" s="5">
-        <v>20424</v>
-      </c>
-      <c r="G8" s="4">
-        <v>1.712</v>
-      </c>
       <c r="H8" s="5">
-        <v>20544</v>
+        <v>15318</v>
       </c>
       <c r="I8" s="4">
+        <v>1.679</v>
+      </c>
+      <c r="J8" s="5">
+        <v>15111</v>
+      </c>
+      <c r="K8" s="4">
+        <v>1.713</v>
+      </c>
+      <c r="L8" s="5">
+        <v>15417</v>
+      </c>
+      <c r="M8" s="4">
+        <v>1.548</v>
+      </c>
+      <c r="N8" s="5">
+        <v>13932</v>
+      </c>
+      <c r="O8" s="4">
         <v>1.694</v>
       </c>
-      <c r="J8" s="5">
-        <v>20328</v>
-      </c>
-      <c r="K8" s="4">
-        <v>1.735</v>
-      </c>
-      <c r="L8" s="5">
-        <v>20820</v>
-      </c>
-      <c r="M8" s="4">
-        <v>1.69</v>
-      </c>
-      <c r="N8" s="5">
-        <v>20280</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="P8" s="5">
+        <v>15246</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>1.704</v>
+      </c>
+      <c r="R8" s="5">
+        <v>15336</v>
+      </c>
+      <c r="S8" s="4">
+        <v>1.557</v>
+      </c>
+      <c r="T8" s="5">
+        <v>14175</v>
+      </c>
+      <c r="U8" s="4">
+        <v>1.699</v>
+      </c>
+      <c r="V8" s="5">
+        <v>15291</v>
+      </c>
+      <c r="W8" s="4">
+        <v>1.79</v>
+      </c>
+      <c r="X8" s="5">
+        <v>16110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C9" s="4">
         <v>0.94</v>
       </c>
       <c r="D9" s="5">
-        <v>28200</v>
+        <v>22560</v>
       </c>
       <c r="E9" s="4">
+        <v>0.968</v>
+      </c>
+      <c r="F9" s="5">
+        <v>23232</v>
+      </c>
+      <c r="G9" s="4">
         <v>0.972</v>
       </c>
-      <c r="F9" s="5">
-        <v>29160</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="H9" s="5">
+        <v>23328</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.958</v>
+      </c>
+      <c r="J9" s="5">
+        <v>22992</v>
+      </c>
+      <c r="K9" s="4">
         <v>0.976</v>
       </c>
-      <c r="H9" s="5">
-        <v>29280</v>
-      </c>
-      <c r="I9" s="4">
-        <v>0.969</v>
-      </c>
-      <c r="J9" s="5">
-        <v>29070</v>
-      </c>
-      <c r="K9" s="4">
-        <v>0.988</v>
-      </c>
       <c r="L9" s="5">
-        <v>29640</v>
+        <v>23424</v>
       </c>
       <c r="M9" s="4">
-        <v>0.965</v>
+        <v>0.91</v>
       </c>
       <c r="N9" s="5">
-        <v>28950</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+        <v>21840</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0.966</v>
+      </c>
+      <c r="P9" s="5">
+        <v>23184</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.952</v>
+      </c>
+      <c r="R9" s="5">
+        <v>22848</v>
+      </c>
+      <c r="S9" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="T9" s="5">
+        <v>21600</v>
+      </c>
+      <c r="U9" s="4">
+        <v>0.963</v>
+      </c>
+      <c r="V9" s="5">
+        <v>23112</v>
+      </c>
+      <c r="W9" s="4">
+        <v>1.012</v>
+      </c>
+      <c r="X9" s="5">
+        <v>24288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D10" s="5">
         <v>1500</v>
       </c>
       <c r="F10" s="5">
+        <v>1950</v>
+      </c>
+      <c r="H10" s="5">
         <v>1600</v>
       </c>
-      <c r="H10" s="5">
+      <c r="J10" s="5">
+        <v>1800</v>
+      </c>
+      <c r="L10" s="5">
         <v>2050</v>
       </c>
-      <c r="J10" s="5">
+      <c r="N10" s="5">
+        <v>1900</v>
+      </c>
+      <c r="P10" s="5">
         <v>1725</v>
       </c>
-      <c r="L10" s="5">
+      <c r="R10" s="5">
         <v>1850</v>
       </c>
-      <c r="N10" s="5">
+      <c r="T10" s="5">
         <v>2400</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="V10" s="5">
+        <v>1650</v>
+      </c>
+      <c r="X10" s="5">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D11" s="7">
         <f>SUM(D5:D10)</f>
-        <v>130500</v>
+        <v>100058</v>
       </c>
       <c r="F11" s="7">
         <f>SUM(F5:F10)</f>
-        <v>132460</v>
+        <v>100045</v>
       </c>
       <c r="H11" s="7">
         <f>SUM(H5:H10)</f>
-        <v>133102</v>
+        <v>100608</v>
       </c>
       <c r="J11" s="7">
         <f>SUM(J5:J10)</f>
-        <v>131895</v>
+        <v>99876</v>
       </c>
       <c r="L11" s="7">
         <f>SUM(L5:L10)</f>
-        <v>144726</v>
+        <v>101214</v>
       </c>
       <c r="N11" s="7">
         <f>SUM(N5:N10)</f>
-        <v>131646</v>
+        <v>94902</v>
+      </c>
+      <c r="P11" s="7">
+        <f>SUM(P5:P10)</f>
+        <v>99567</v>
+      </c>
+      <c r="R11" s="7">
+        <f>SUM(R5:R10)</f>
+        <v>101839</v>
+      </c>
+      <c r="T11" s="7">
+        <f>SUM(T5:T10)</f>
+        <v>93499</v>
+      </c>
+      <c r="V11" s="7">
+        <f>SUM(V5:V10)</f>
+        <v>100868</v>
+      </c>
+      <c r="X11" s="7">
+        <f>SUM(X5:X10)</f>
+        <v>105877</v>
       </c>
     </row>
   </sheetData>
@@ -1067,254 +1387,411 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
     <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="A3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="10"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="A4" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" s="10"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="A5" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="E5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>48</v>
       </c>
+      <c r="G5" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="10"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="D9" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="I9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>71</v>
-      </c>
+      <c r="D12" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1330,102 +1807,102 @@
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B4" s="8">
         <v>3.4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B5" s="8">
-        <v>4.85</v>
+        <v>4.87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B6" s="8">
         <v>5.1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B7" s="8">
         <v>5.6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B8" s="8">
         <v>4.2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B9" s="8">
         <v>4.6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="B10" s="8">
         <v>5.35</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1435,188 +1912,263 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
+      <c r="B3" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="I3" s="10"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="10">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="8">
+      <c r="B4" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="11">
         <v>0.9</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="10">
         <v>400</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="10">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="10">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" s="8">
+      <c r="B5" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.61</v>
+      </c>
+      <c r="G5" s="10">
+        <v>500</v>
+      </c>
+      <c r="H5" s="10">
+        <v>26</v>
+      </c>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="10">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="11">
         <v>0.55</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G6" s="10">
         <v>600</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H6" s="10">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="10">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="B7" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="11">
         <v>0.3</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G7" s="10">
         <v>1200</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H7" s="10">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="10">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="8">
+      <c r="B8" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F8" s="11">
         <v>2.6</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G8" s="10">
         <v>150</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H8" s="10">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="10">
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="B9" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F9" s="11">
         <v>1.4</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G9" s="10">
         <v>250</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H9" s="10">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
+      <c r="I9" s="10"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="10">
         <v>5</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="B10" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" s="11">
         <v>1.65</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G10" s="10">
         <v>250</v>
       </c>
-      <c r="G9" s="2">
+      <c r="H10" s="10">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>103</v>
-      </c>
+      <c r="I10" s="10"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/submissions/10-carton-bid-evaluation/inputs/bid_tabulation_itb_2026_17.xlsx
+++ b/submissions/10-carton-bid-evaluation/inputs/bid_tabulation_itb_2026_17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D5DAD6-4945-5741-B597-FC2D3FEDF328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C2FF05-A3AC-7843-A4DC-25EBC94C0EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -198,9 +198,6 @@
     <t>1% 30, net 45</t>
   </si>
   <si>
-    <t>Cashier's check, $4,904.75, no. 20871</t>
-  </si>
-  <si>
     <t>1, 2</t>
   </si>
   <si>
@@ -276,7 +273,10 @@
     <t>Ridgecrest Packaging</t>
   </si>
   <si>
-    <t>Cedar Rapids</t>
+    <t>Omaha</t>
+  </si>
+  <si>
+    <t>NE</t>
   </si>
   <si>
     <t>Origin, shipping plant</t>
@@ -285,6 +285,9 @@
     <t>1% 20, net 45</t>
   </si>
   <si>
+    <t>Cashier's check, $4,554.95, no. 7730412</t>
+  </si>
+  <si>
     <t>Thorsgard Box &amp; Label</t>
   </si>
   <si>
@@ -337,9 +340,6 @@
   </si>
   <si>
     <t>Common carrier, Sioux Falls gateway</t>
-  </si>
-  <si>
-    <t>NE</t>
   </si>
   <si>
     <t>Common carrier, Omaha gateway</t>
@@ -937,10 +937,10 @@
         <v>25695</v>
       </c>
       <c r="E5" s="4">
-        <v>0.591</v>
+        <v>0.597</v>
       </c>
       <c r="F5" s="5">
-        <v>26595</v>
+        <v>26865</v>
       </c>
       <c r="G5" s="4">
         <v>0.594</v>
@@ -1011,10 +1011,10 @@
         <v>25472</v>
       </c>
       <c r="E6" s="4">
-        <v>0.397</v>
+        <v>0.4</v>
       </c>
       <c r="F6" s="5">
-        <v>25408</v>
+        <v>25900</v>
       </c>
       <c r="G6" s="4">
         <v>0.404</v>
@@ -1159,10 +1159,10 @@
         <v>14895</v>
       </c>
       <c r="E8" s="4">
-        <v>1.688</v>
+        <v>1.702</v>
       </c>
       <c r="F8" s="5">
-        <v>15192</v>
+        <v>15318</v>
       </c>
       <c r="G8" s="4">
         <v>1.702</v>
@@ -1233,10 +1233,10 @@
         <v>22560</v>
       </c>
       <c r="E9" s="4">
-        <v>0.968</v>
+        <v>0.984</v>
       </c>
       <c r="F9" s="5">
-        <v>23232</v>
+        <v>23616</v>
       </c>
       <c r="G9" s="4">
         <v>0.972</v>
@@ -1269,10 +1269,10 @@
         <v>23184</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.952</v>
+        <v>0.957</v>
       </c>
       <c r="R9" s="5">
-        <v>22848</v>
+        <v>22968</v>
       </c>
       <c r="S9" s="4">
         <v>0.9</v>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="F11" s="7">
         <f>SUM(F5:F10)</f>
-        <v>100045</v>
+        <v>101317</v>
       </c>
       <c r="H11" s="7">
         <f>SUM(H5:H10)</f>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="R11" s="7">
         <f>SUM(R5:R10)</f>
-        <v>101839</v>
+        <v>101959</v>
       </c>
       <c r="T11" s="7">
         <f>SUM(T5:T10)</f>
@@ -1487,10 +1487,10 @@
         <v>48</v>
       </c>
       <c r="G5" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>48</v>
@@ -1499,19 +1499,19 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="C6" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>46</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>48</v>
@@ -1520,7 +1520,7 @@
         <v>49</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>48</v>
@@ -1529,19 +1529,19 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="C7" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>63</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>46</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>48</v>
@@ -1550,7 +1550,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>48</v>
@@ -1559,28 +1559,28 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="C8" s="10" t="s">
         <v>66</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>67</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>46</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>48</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>48</v>
@@ -1589,19 +1589,19 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>48</v>
@@ -1610,7 +1610,7 @@
         <v>49</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>48</v>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>53</v>
@@ -1631,7 +1631,7 @@
         <v>46</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>48</v>
@@ -1640,7 +1640,7 @@
         <v>49</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>48</v>
@@ -1649,19 +1649,19 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="C11" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>48</v>
@@ -1670,7 +1670,7 @@
         <v>49</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>48</v>
@@ -1679,13 +1679,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="C12" s="10" t="s">
         <v>81</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>63</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>82</v>
@@ -1697,10 +1697,10 @@
         <v>48</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>48</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>53</v>
@@ -1721,7 +1721,7 @@
         <v>46</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>48</v>
@@ -1730,7 +1730,7 @@
         <v>49</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>48</v>
@@ -1739,28 +1739,28 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>46</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>48</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>48</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -1809,18 +1809,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1831,29 +1831,29 @@
         <v>3.4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" s="8">
         <v>4.87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" s="8">
         <v>5.1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1864,34 +1864,34 @@
         <v>5.6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="8">
         <v>4.2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="8">
         <v>4.6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="B10" s="8">
         <v>5.35</v>

--- a/submissions/10-carton-bid-evaluation/inputs/bid_tabulation_itb_2026_17.xlsx
+++ b/submissions/10-carton-bid-evaluation/inputs/bid_tabulation_itb_2026_17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C2FF05-A3AC-7843-A4DC-25EBC94C0EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13506D2-35E9-B147-8718-3F49CA7856EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="130">
   <si>
     <t>ITB 2026-17, corrugated shipping cartons, annual requirement; bids as opened October 6, 2026, 10:00, Nordvik Manufacturing purchasing office</t>
   </si>
@@ -195,7 +195,10 @@
     <t>MN</t>
   </si>
   <si>
-    <t>1% 30, net 45</t>
+    <t>Origin, shipping plant</t>
+  </si>
+  <si>
+    <t>2% 10, net 30</t>
   </si>
   <si>
     <t>1, 2</t>
@@ -267,9 +270,6 @@
     <t>WI</t>
   </si>
   <si>
-    <t>2% 10, net 30</t>
-  </si>
-  <si>
     <t>Ridgecrest Packaging</t>
   </si>
   <si>
@@ -277,9 +277,6 @@
   </si>
   <si>
     <t>NE</t>
-  </si>
-  <si>
-    <t>Origin, shipping plant</t>
   </si>
   <si>
     <t>1% 20, net 45</t>
@@ -937,10 +934,10 @@
         <v>25695</v>
       </c>
       <c r="E5" s="4">
-        <v>0.597</v>
+        <v>0.551</v>
       </c>
       <c r="F5" s="5">
-        <v>26865</v>
+        <v>24795</v>
       </c>
       <c r="G5" s="4">
         <v>0.594</v>
@@ -1011,10 +1008,10 @@
         <v>25472</v>
       </c>
       <c r="E6" s="4">
-        <v>0.4</v>
+        <v>0.371</v>
       </c>
       <c r="F6" s="5">
-        <v>25900</v>
+        <v>24044</v>
       </c>
       <c r="G6" s="4">
         <v>0.404</v>
@@ -1085,10 +1082,10 @@
         <v>9936</v>
       </c>
       <c r="E7" s="4">
-        <v>0.284</v>
+        <v>0.263</v>
       </c>
       <c r="F7" s="5">
-        <v>7668</v>
+        <v>7101</v>
       </c>
       <c r="G7" s="4">
         <v>0.288</v>
@@ -1159,10 +1156,10 @@
         <v>14895</v>
       </c>
       <c r="E8" s="4">
-        <v>1.702</v>
+        <v>1.576</v>
       </c>
       <c r="F8" s="5">
-        <v>15318</v>
+        <v>14184</v>
       </c>
       <c r="G8" s="4">
         <v>1.702</v>
@@ -1233,10 +1230,10 @@
         <v>22560</v>
       </c>
       <c r="E9" s="4">
-        <v>0.984</v>
+        <v>0.911</v>
       </c>
       <c r="F9" s="5">
-        <v>23616</v>
+        <v>21864</v>
       </c>
       <c r="G9" s="4">
         <v>0.972</v>
@@ -1269,10 +1266,10 @@
         <v>23184</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.957</v>
+        <v>0.985</v>
       </c>
       <c r="R9" s="5">
-        <v>22968</v>
+        <v>23640</v>
       </c>
       <c r="S9" s="4">
         <v>0.9</v>
@@ -1341,7 +1338,7 @@
       </c>
       <c r="F11" s="7">
         <f>SUM(F5:F10)</f>
-        <v>101317</v>
+        <v>93938</v>
       </c>
       <c r="H11" s="7">
         <f>SUM(H5:H10)</f>
@@ -1365,7 +1362,7 @@
       </c>
       <c r="R11" s="7">
         <f>SUM(R5:R10)</f>
-        <v>101959</v>
+        <v>102631</v>
       </c>
       <c r="T11" s="7">
         <f>SUM(T5:T10)</f>
@@ -1478,10 +1475,10 @@
         <v>53</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>48</v>
@@ -1490,7 +1487,7 @@
         <v>49</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>48</v>
@@ -1499,19 +1496,19 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>46</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>48</v>
@@ -1520,7 +1517,7 @@
         <v>49</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>48</v>
@@ -1529,19 +1526,19 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>46</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>48</v>
@@ -1550,7 +1547,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>48</v>
@@ -1559,28 +1556,28 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>46</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>48</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>48</v>
@@ -1589,19 +1586,19 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>48</v>
@@ -1610,7 +1607,7 @@
         <v>49</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>48</v>
@@ -1619,10 +1616,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>53</v>
@@ -1631,7 +1628,7 @@
         <v>46</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>48</v>
@@ -1640,7 +1637,7 @@
         <v>49</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>48</v>
@@ -1649,19 +1646,19 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>46</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>48</v>
@@ -1670,7 +1667,7 @@
         <v>49</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>48</v>
@@ -1688,19 +1685,19 @@
         <v>81</v>
       </c>
       <c r="D12" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>48</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>48</v>
@@ -1709,10 +1706,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>86</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>53</v>
@@ -1721,7 +1718,7 @@
         <v>46</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>48</v>
@@ -1730,7 +1727,7 @@
         <v>49</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>48</v>
@@ -1739,28 +1736,28 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>89</v>
-      </c>
       <c r="C14" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>46</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>48</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>48</v>
@@ -1781,7 +1778,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -1809,18 +1806,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1831,29 +1828,29 @@
         <v>3.4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="8">
         <v>4.87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B6" s="8">
         <v>5.1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1864,29 +1861,29 @@
         <v>5.6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" s="8">
         <v>4.2</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="8">
         <v>4.6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1897,12 +1894,12 @@
         <v>5.35</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1927,7 +1924,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -1935,25 +1932,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="G3" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="I3" s="10"/>
     </row>
@@ -1962,16 +1959,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="F4" s="11">
         <v>0.9</v>
@@ -1989,16 +1986,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="F5" s="11">
         <v>0.61</v>
@@ -2016,16 +2013,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="F6" s="11">
         <v>0.55</v>
@@ -2043,16 +2040,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="F7" s="11">
         <v>0.3</v>
@@ -2070,16 +2067,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="F8" s="11">
         <v>2.6</v>
@@ -2097,16 +2094,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="F9" s="11">
         <v>1.4</v>
@@ -2124,16 +2121,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>128</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="F10" s="11">
         <v>1.65</v>
@@ -2159,7 +2156,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
